--- a/src/Excelsior.Tests/TemplateSheetTests.RequiredHighlighting.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.RequiredHighlighting.verified.xlsx
@@ -94,5 +94,13 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A26">
+      <formula1>LEN(TRIM(A2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C26">
+      <formula1>LEN(TRIM(C2))&gt;0</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/TemplateSheetTests.RequiredHighlighting.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.RequiredHighlighting.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -103,4 +103,14 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Employees">
+    <column index="1" property="Name"/>
+    <column index="2" property="Email"/>
+    <column index="3" property="HireDate"/>
+  </sheet>
+</columnMetadata>
 </file>